--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="154">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t>['45+3', '50']</t>
+  </si>
+  <si>
+    <t>['49']</t>
   </si>
   <si>
     <t>['34', '45+4', '46']</t>
@@ -834,7 +837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP66"/>
+  <dimension ref="A1:BP67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1090,7 +1093,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1296,7 +1299,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1914,7 +1917,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2120,7 +2123,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2326,7 +2329,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2738,7 +2741,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -2944,7 +2947,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3356,7 +3359,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3562,7 +3565,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3768,7 +3771,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -3974,7 +3977,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4258,7 +4261,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ17">
         <v>1.33</v>
@@ -4673,7 +4676,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ19">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -4798,7 +4801,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5004,7 +5007,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5210,7 +5213,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q22">
         <v>1.91</v>
@@ -5622,7 +5625,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5828,7 +5831,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6858,7 +6861,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7064,7 +7067,7 @@
         <v>89</v>
       </c>
       <c r="P31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7348,7 +7351,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ32">
         <v>2</v>
@@ -7763,7 +7766,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ34">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR34">
         <v>0.6899999999999999</v>
@@ -7888,7 +7891,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8300,7 +8303,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8918,7 +8921,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9124,7 +9127,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9536,7 +9539,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9948,7 +9951,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10360,7 +10363,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10772,7 +10775,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11184,7 +11187,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11262,7 +11265,7 @@
         <v>0.67</v>
       </c>
       <c r="AP51">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AQ51">
         <v>1.6</v>
@@ -11390,7 +11393,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11596,7 +11599,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12420,7 +12423,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12832,7 +12835,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13244,7 +13247,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13531,7 +13534,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ62">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR62">
         <v>1.35</v>
@@ -14274,7 +14277,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14431,6 +14434,212 @@
       </c>
       <c r="BP66">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="67" spans="1:68">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>7729600</v>
+      </c>
+      <c r="C67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="2">
+        <v>45668.45833333334</v>
+      </c>
+      <c r="F67">
+        <v>8</v>
+      </c>
+      <c r="G67" t="s">
+        <v>85</v>
+      </c>
+      <c r="H67" t="s">
+        <v>77</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="O67" t="s">
+        <v>122</v>
+      </c>
+      <c r="P67" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q67">
+        <v>2.63</v>
+      </c>
+      <c r="R67">
+        <v>1.8</v>
+      </c>
+      <c r="S67">
+        <v>6</v>
+      </c>
+      <c r="T67">
+        <v>1.63</v>
+      </c>
+      <c r="U67">
+        <v>2.16</v>
+      </c>
+      <c r="V67">
+        <v>3.62</v>
+      </c>
+      <c r="W67">
+        <v>1.26</v>
+      </c>
+      <c r="X67">
+        <v>10.2</v>
+      </c>
+      <c r="Y67">
+        <v>1.03</v>
+      </c>
+      <c r="Z67">
+        <v>1.82</v>
+      </c>
+      <c r="AA67">
+        <v>3.1</v>
+      </c>
+      <c r="AB67">
+        <v>4.6</v>
+      </c>
+      <c r="AC67">
+        <v>1.1</v>
+      </c>
+      <c r="AD67">
+        <v>5.2</v>
+      </c>
+      <c r="AE67">
+        <v>1.52</v>
+      </c>
+      <c r="AF67">
+        <v>2.38</v>
+      </c>
+      <c r="AG67">
+        <v>2.45</v>
+      </c>
+      <c r="AH67">
+        <v>1.49</v>
+      </c>
+      <c r="AI67">
+        <v>2.75</v>
+      </c>
+      <c r="AJ67">
+        <v>1.4</v>
+      </c>
+      <c r="AK67">
+        <v>1.25</v>
+      </c>
+      <c r="AL67">
+        <v>1.32</v>
+      </c>
+      <c r="AM67">
+        <v>1.6</v>
+      </c>
+      <c r="AN67">
+        <v>0.67</v>
+      </c>
+      <c r="AO67">
+        <v>0.33</v>
+      </c>
+      <c r="AP67">
+        <v>1.25</v>
+      </c>
+      <c r="AQ67">
+        <v>0.25</v>
+      </c>
+      <c r="AR67">
+        <v>1.03</v>
+      </c>
+      <c r="AS67">
+        <v>0.98</v>
+      </c>
+      <c r="AT67">
+        <v>2.01</v>
+      </c>
+      <c r="AU67">
+        <v>2</v>
+      </c>
+      <c r="AV67">
+        <v>0</v>
+      </c>
+      <c r="AW67">
+        <v>6</v>
+      </c>
+      <c r="AX67">
+        <v>9</v>
+      </c>
+      <c r="AY67">
+        <v>8</v>
+      </c>
+      <c r="AZ67">
+        <v>9</v>
+      </c>
+      <c r="BA67">
+        <v>6</v>
+      </c>
+      <c r="BB67">
+        <v>7</v>
+      </c>
+      <c r="BC67">
+        <v>13</v>
+      </c>
+      <c r="BD67">
+        <v>1.6</v>
+      </c>
+      <c r="BE67">
+        <v>7.9</v>
+      </c>
+      <c r="BF67">
+        <v>2.73</v>
+      </c>
+      <c r="BG67">
+        <v>1.25</v>
+      </c>
+      <c r="BH67">
+        <v>3.28</v>
+      </c>
+      <c r="BI67">
+        <v>1.48</v>
+      </c>
+      <c r="BJ67">
+        <v>2.33</v>
+      </c>
+      <c r="BK67">
+        <v>1.84</v>
+      </c>
+      <c r="BL67">
+        <v>1.82</v>
+      </c>
+      <c r="BM67">
+        <v>2.35</v>
+      </c>
+      <c r="BN67">
+        <v>1.47</v>
+      </c>
+      <c r="BO67">
+        <v>3.2</v>
+      </c>
+      <c r="BP67">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="155">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -476,6 +476,9 @@
   </si>
   <si>
     <t>['81']</t>
+  </si>
+  <si>
+    <t>['33']</t>
   </si>
 </sst>
 </file>
@@ -837,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP67"/>
+  <dimension ref="A1:BP68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1586,7 +1589,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -3231,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ12">
         <v>0.33</v>
@@ -6324,7 +6327,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ27">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR27">
         <v>2</v>
@@ -7145,7 +7148,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ31">
         <v>2</v>
@@ -9620,7 +9623,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ43">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR43">
         <v>1.52</v>
@@ -10647,7 +10650,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ48">
         <v>0.67</v>
@@ -14640,6 +14643,212 @@
       </c>
       <c r="BP67">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="68" spans="1:68">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>7729601</v>
+      </c>
+      <c r="C68" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" t="s">
+        <v>69</v>
+      </c>
+      <c r="E68" s="2">
+        <v>45668.58333333334</v>
+      </c>
+      <c r="F68">
+        <v>8</v>
+      </c>
+      <c r="G68" t="s">
+        <v>80</v>
+      </c>
+      <c r="H68" t="s">
+        <v>81</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68" t="s">
+        <v>89</v>
+      </c>
+      <c r="P68" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q68">
+        <v>4</v>
+      </c>
+      <c r="R68">
+        <v>1.8</v>
+      </c>
+      <c r="S68">
+        <v>3.2</v>
+      </c>
+      <c r="T68">
+        <v>1.74</v>
+      </c>
+      <c r="U68">
+        <v>2</v>
+      </c>
+      <c r="V68">
+        <v>3.9</v>
+      </c>
+      <c r="W68">
+        <v>1.23</v>
+      </c>
+      <c r="X68">
+        <v>10.25</v>
+      </c>
+      <c r="Y68">
+        <v>1.03</v>
+      </c>
+      <c r="Z68">
+        <v>3.75</v>
+      </c>
+      <c r="AA68">
+        <v>2.5</v>
+      </c>
+      <c r="AB68">
+        <v>2.35</v>
+      </c>
+      <c r="AC68">
+        <v>1.15</v>
+      </c>
+      <c r="AD68">
+        <v>3.95</v>
+      </c>
+      <c r="AE68">
+        <v>1.63</v>
+      </c>
+      <c r="AF68">
+        <v>2.19</v>
+      </c>
+      <c r="AG68">
+        <v>3.25</v>
+      </c>
+      <c r="AH68">
+        <v>1.33</v>
+      </c>
+      <c r="AI68">
+        <v>2.25</v>
+      </c>
+      <c r="AJ68">
+        <v>1.57</v>
+      </c>
+      <c r="AK68">
+        <v>1.49</v>
+      </c>
+      <c r="AL68">
+        <v>1.42</v>
+      </c>
+      <c r="AM68">
+        <v>1.24</v>
+      </c>
+      <c r="AN68">
+        <v>1.33</v>
+      </c>
+      <c r="AO68">
+        <v>1.67</v>
+      </c>
+      <c r="AP68">
+        <v>1</v>
+      </c>
+      <c r="AQ68">
+        <v>2</v>
+      </c>
+      <c r="AR68">
+        <v>0.92</v>
+      </c>
+      <c r="AS68">
+        <v>1.23</v>
+      </c>
+      <c r="AT68">
+        <v>2.15</v>
+      </c>
+      <c r="AU68">
+        <v>0</v>
+      </c>
+      <c r="AV68">
+        <v>7</v>
+      </c>
+      <c r="AW68">
+        <v>5</v>
+      </c>
+      <c r="AX68">
+        <v>8</v>
+      </c>
+      <c r="AY68">
+        <v>5</v>
+      </c>
+      <c r="AZ68">
+        <v>15</v>
+      </c>
+      <c r="BA68">
+        <v>3</v>
+      </c>
+      <c r="BB68">
+        <v>9</v>
+      </c>
+      <c r="BC68">
+        <v>12</v>
+      </c>
+      <c r="BD68">
+        <v>2.38</v>
+      </c>
+      <c r="BE68">
+        <v>5.95</v>
+      </c>
+      <c r="BF68">
+        <v>1.89</v>
+      </c>
+      <c r="BG68">
+        <v>1.38</v>
+      </c>
+      <c r="BH68">
+        <v>2.62</v>
+      </c>
+      <c r="BI68">
+        <v>1.72</v>
+      </c>
+      <c r="BJ68">
+        <v>1.95</v>
+      </c>
+      <c r="BK68">
+        <v>2.19</v>
+      </c>
+      <c r="BL68">
+        <v>1.54</v>
+      </c>
+      <c r="BM68">
+        <v>2.97</v>
+      </c>
+      <c r="BN68">
+        <v>1.3</v>
+      </c>
+      <c r="BO68">
+        <v>3.8</v>
+      </c>
+      <c r="BP68">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="155">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -840,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP68"/>
+  <dimension ref="A1:BP69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ14">
         <v>2.33</v>
@@ -3855,7 +3855,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ15">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -6945,7 +6945,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ30">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR30">
         <v>1.49</v>
@@ -7560,7 +7560,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ33">
         <v>0.67</v>
@@ -10653,7 +10653,7 @@
         <v>1</v>
       </c>
       <c r="AQ48">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR48">
         <v>0.85</v>
@@ -11474,7 +11474,7 @@
         <v>2</v>
       </c>
       <c r="AP52">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AQ52">
         <v>2.33</v>
@@ -14167,22 +14167,22 @@
         <v>3.19</v>
       </c>
       <c r="AU65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV65">
         <v>4</v>
       </c>
       <c r="AW65">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY65">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ65">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BA65">
         <v>4</v>
@@ -14379,13 +14379,13 @@
         <v>2</v>
       </c>
       <c r="AW66">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AX66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY66">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ66">
         <v>5</v>
@@ -14579,7 +14579,7 @@
         <v>2.01</v>
       </c>
       <c r="AU67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV67">
         <v>0</v>
@@ -14588,13 +14588,13 @@
         <v>6</v>
       </c>
       <c r="AX67">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY67">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AZ67">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA67">
         <v>6</v>
@@ -14788,19 +14788,19 @@
         <v>0</v>
       </c>
       <c r="AV68">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX68">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY68">
         <v>5</v>
       </c>
       <c r="AZ68">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA68">
         <v>3</v>
@@ -14849,6 +14849,212 @@
       </c>
       <c r="BP68">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:68">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>7729598</v>
+      </c>
+      <c r="C69" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="2">
+        <v>45669.58333333334</v>
+      </c>
+      <c r="F69">
+        <v>8</v>
+      </c>
+      <c r="G69" t="s">
+        <v>82</v>
+      </c>
+      <c r="H69" t="s">
+        <v>73</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>1</v>
+      </c>
+      <c r="O69" t="s">
+        <v>97</v>
+      </c>
+      <c r="P69" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q69">
+        <v>3.1</v>
+      </c>
+      <c r="R69">
+        <v>1.8</v>
+      </c>
+      <c r="S69">
+        <v>4.33</v>
+      </c>
+      <c r="T69">
+        <v>1.75</v>
+      </c>
+      <c r="U69">
+        <v>1.99</v>
+      </c>
+      <c r="V69">
+        <v>4</v>
+      </c>
+      <c r="W69">
+        <v>1.22</v>
+      </c>
+      <c r="X69">
+        <v>10.2</v>
+      </c>
+      <c r="Y69">
+        <v>1.03</v>
+      </c>
+      <c r="Z69">
+        <v>2.2</v>
+      </c>
+      <c r="AA69">
+        <v>2.75</v>
+      </c>
+      <c r="AB69">
+        <v>3.6</v>
+      </c>
+      <c r="AC69">
+        <v>1.14</v>
+      </c>
+      <c r="AD69">
+        <v>4.1</v>
+      </c>
+      <c r="AE69">
+        <v>1.64</v>
+      </c>
+      <c r="AF69">
+        <v>2.17</v>
+      </c>
+      <c r="AG69">
+        <v>3</v>
+      </c>
+      <c r="AH69">
+        <v>1.36</v>
+      </c>
+      <c r="AI69">
+        <v>2.38</v>
+      </c>
+      <c r="AJ69">
+        <v>1.53</v>
+      </c>
+      <c r="AK69">
+        <v>1.23</v>
+      </c>
+      <c r="AL69">
+        <v>1.38</v>
+      </c>
+      <c r="AM69">
+        <v>1.56</v>
+      </c>
+      <c r="AN69">
+        <v>0.33</v>
+      </c>
+      <c r="AO69">
+        <v>0.67</v>
+      </c>
+      <c r="AP69">
+        <v>1</v>
+      </c>
+      <c r="AQ69">
+        <v>0.5</v>
+      </c>
+      <c r="AR69">
+        <v>1.78</v>
+      </c>
+      <c r="AS69">
+        <v>1.29</v>
+      </c>
+      <c r="AT69">
+        <v>3.07</v>
+      </c>
+      <c r="AU69">
+        <v>4</v>
+      </c>
+      <c r="AV69">
+        <v>0</v>
+      </c>
+      <c r="AW69">
+        <v>4</v>
+      </c>
+      <c r="AX69">
+        <v>8</v>
+      </c>
+      <c r="AY69">
+        <v>8</v>
+      </c>
+      <c r="AZ69">
+        <v>8</v>
+      </c>
+      <c r="BA69">
+        <v>2</v>
+      </c>
+      <c r="BB69">
+        <v>7</v>
+      </c>
+      <c r="BC69">
+        <v>9</v>
+      </c>
+      <c r="BD69">
+        <v>1.52</v>
+      </c>
+      <c r="BE69">
+        <v>6.2</v>
+      </c>
+      <c r="BF69">
+        <v>3.15</v>
+      </c>
+      <c r="BG69">
+        <v>1.26</v>
+      </c>
+      <c r="BH69">
+        <v>3.5</v>
+      </c>
+      <c r="BI69">
+        <v>1.48</v>
+      </c>
+      <c r="BJ69">
+        <v>2.45</v>
+      </c>
+      <c r="BK69">
+        <v>2.38</v>
+      </c>
+      <c r="BL69">
+        <v>1.9</v>
+      </c>
+      <c r="BM69">
+        <v>2.43</v>
+      </c>
+      <c r="BN69">
+        <v>1.49</v>
+      </c>
+      <c r="BO69">
+        <v>3.35</v>
+      </c>
+      <c r="BP69">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="157">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -383,6 +383,12 @@
   </si>
   <si>
     <t>['49']</t>
+  </si>
+  <si>
+    <t>['34', '51', '84']</t>
+  </si>
+  <si>
+    <t>['62', '90+1']</t>
   </si>
   <si>
     <t>['34', '45+4', '46']</t>
@@ -840,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP69"/>
+  <dimension ref="A1:BP71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1096,7 +1102,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1302,7 +1308,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1920,7 +1926,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2126,7 +2132,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2204,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ7">
         <v>1.25</v>
@@ -2332,7 +2338,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2619,7 +2625,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2744,7 +2750,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -2822,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ10">
         <v>1.6</v>
@@ -2950,7 +2956,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3362,7 +3368,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3568,7 +3574,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3774,7 +3780,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -3980,7 +3986,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4473,7 +4479,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ18">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4804,7 +4810,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5010,7 +5016,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5088,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ21">
         <v>1.5</v>
@@ -5216,7 +5222,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q22">
         <v>1.91</v>
@@ -5294,7 +5300,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ22">
         <v>1.25</v>
@@ -5628,7 +5634,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5709,7 +5715,7 @@
         <v>1</v>
       </c>
       <c r="AQ24">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR24">
         <v>1.3</v>
@@ -5834,7 +5840,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6864,7 +6870,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7070,7 +7076,7 @@
         <v>89</v>
       </c>
       <c r="P31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7563,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="AQ33">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR33">
         <v>1.75</v>
@@ -7894,7 +7900,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8306,7 +8312,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8924,7 +8930,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9130,7 +9136,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9542,7 +9548,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9954,7 +9960,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10366,7 +10372,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10778,7 +10784,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11062,7 +11068,7 @@
         <v>2</v>
       </c>
       <c r="AP50">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ50">
         <v>1.33</v>
@@ -11190,7 +11196,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11396,7 +11402,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11477,7 +11483,7 @@
         <v>1</v>
       </c>
       <c r="AQ52">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR52">
         <v>1.77</v>
@@ -11602,7 +11608,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -11889,7 +11895,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ54">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AR54">
         <v>1.9</v>
@@ -12426,7 +12432,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12838,7 +12844,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13250,7 +13256,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13946,7 +13952,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14280,7 +14286,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14692,7 +14698,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15055,6 +15061,418 @@
       </c>
       <c r="BP69">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:68">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>7729602</v>
+      </c>
+      <c r="C70" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" t="s">
+        <v>69</v>
+      </c>
+      <c r="E70" s="2">
+        <v>45672.45833333334</v>
+      </c>
+      <c r="F70">
+        <v>8</v>
+      </c>
+      <c r="G70" t="s">
+        <v>75</v>
+      </c>
+      <c r="H70" t="s">
+        <v>79</v>
+      </c>
+      <c r="I70">
+        <v>1</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <v>3</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>3</v>
+      </c>
+      <c r="O70" t="s">
+        <v>123</v>
+      </c>
+      <c r="P70" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q70">
+        <v>2</v>
+      </c>
+      <c r="R70">
+        <v>2.1</v>
+      </c>
+      <c r="S70">
+        <v>7</v>
+      </c>
+      <c r="T70">
+        <v>1.44</v>
+      </c>
+      <c r="U70">
+        <v>2.6</v>
+      </c>
+      <c r="V70">
+        <v>2.75</v>
+      </c>
+      <c r="W70">
+        <v>1.4</v>
+      </c>
+      <c r="X70">
+        <v>7</v>
+      </c>
+      <c r="Y70">
+        <v>1.1</v>
+      </c>
+      <c r="Z70">
+        <v>1.34</v>
+      </c>
+      <c r="AA70">
+        <v>4.12</v>
+      </c>
+      <c r="AB70">
+        <v>7.5</v>
+      </c>
+      <c r="AC70">
+        <v>1.01</v>
+      </c>
+      <c r="AD70">
+        <v>8.9</v>
+      </c>
+      <c r="AE70">
+        <v>1.32</v>
+      </c>
+      <c r="AF70">
+        <v>3.2</v>
+      </c>
+      <c r="AG70">
+        <v>1.95</v>
+      </c>
+      <c r="AH70">
+        <v>1.75</v>
+      </c>
+      <c r="AI70">
+        <v>2.38</v>
+      </c>
+      <c r="AJ70">
+        <v>1.53</v>
+      </c>
+      <c r="AK70">
+        <v>1.07</v>
+      </c>
+      <c r="AL70">
+        <v>1.17</v>
+      </c>
+      <c r="AM70">
+        <v>2.48</v>
+      </c>
+      <c r="AN70">
+        <v>2.33</v>
+      </c>
+      <c r="AO70">
+        <v>2.33</v>
+      </c>
+      <c r="AP70">
+        <v>2.5</v>
+      </c>
+      <c r="AQ70">
+        <v>1.75</v>
+      </c>
+      <c r="AR70">
+        <v>1.68</v>
+      </c>
+      <c r="AS70">
+        <v>1.08</v>
+      </c>
+      <c r="AT70">
+        <v>2.76</v>
+      </c>
+      <c r="AU70">
+        <v>10</v>
+      </c>
+      <c r="AV70">
+        <v>0</v>
+      </c>
+      <c r="AW70">
+        <v>11</v>
+      </c>
+      <c r="AX70">
+        <v>8</v>
+      </c>
+      <c r="AY70">
+        <v>21</v>
+      </c>
+      <c r="AZ70">
+        <v>8</v>
+      </c>
+      <c r="BA70">
+        <v>8</v>
+      </c>
+      <c r="BB70">
+        <v>1</v>
+      </c>
+      <c r="BC70">
+        <v>9</v>
+      </c>
+      <c r="BD70">
+        <v>1.21</v>
+      </c>
+      <c r="BE70">
+        <v>10.5</v>
+      </c>
+      <c r="BF70">
+        <v>5.96</v>
+      </c>
+      <c r="BG70">
+        <v>1.35</v>
+      </c>
+      <c r="BH70">
+        <v>3.05</v>
+      </c>
+      <c r="BI70">
+        <v>1.6</v>
+      </c>
+      <c r="BJ70">
+        <v>2.28</v>
+      </c>
+      <c r="BK70">
+        <v>2.01</v>
+      </c>
+      <c r="BL70">
+        <v>1.79</v>
+      </c>
+      <c r="BM70">
+        <v>2.61</v>
+      </c>
+      <c r="BN70">
+        <v>1.47</v>
+      </c>
+      <c r="BO70">
+        <v>3.48</v>
+      </c>
+      <c r="BP70">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="71" spans="1:68">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>7729603</v>
+      </c>
+      <c r="C71" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="2">
+        <v>45672.58333333334</v>
+      </c>
+      <c r="F71">
+        <v>8</v>
+      </c>
+      <c r="G71" t="s">
+        <v>78</v>
+      </c>
+      <c r="H71" t="s">
+        <v>72</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>2</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>2</v>
+      </c>
+      <c r="O71" t="s">
+        <v>124</v>
+      </c>
+      <c r="P71" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q71">
+        <v>1.67</v>
+      </c>
+      <c r="R71">
+        <v>2.38</v>
+      </c>
+      <c r="S71">
+        <v>11</v>
+      </c>
+      <c r="T71">
+        <v>1.44</v>
+      </c>
+      <c r="U71">
+        <v>2.6</v>
+      </c>
+      <c r="V71">
+        <v>2.7</v>
+      </c>
+      <c r="W71">
+        <v>1.44</v>
+      </c>
+      <c r="X71">
+        <v>7</v>
+      </c>
+      <c r="Y71">
+        <v>1.1</v>
+      </c>
+      <c r="Z71">
+        <v>1.22</v>
+      </c>
+      <c r="AA71">
+        <v>5.25</v>
+      </c>
+      <c r="AB71">
+        <v>13</v>
+      </c>
+      <c r="AC71">
+        <v>1.01</v>
+      </c>
+      <c r="AD71">
+        <v>8.5</v>
+      </c>
+      <c r="AE71">
+        <v>1.32</v>
+      </c>
+      <c r="AF71">
+        <v>3.2</v>
+      </c>
+      <c r="AG71">
+        <v>1.95</v>
+      </c>
+      <c r="AH71">
+        <v>1.85</v>
+      </c>
+      <c r="AI71">
+        <v>2.75</v>
+      </c>
+      <c r="AJ71">
+        <v>1.4</v>
+      </c>
+      <c r="AK71">
+        <v>1.03</v>
+      </c>
+      <c r="AL71">
+        <v>1.12</v>
+      </c>
+      <c r="AM71">
+        <v>3.05</v>
+      </c>
+      <c r="AN71">
+        <v>2.33</v>
+      </c>
+      <c r="AO71">
+        <v>0.67</v>
+      </c>
+      <c r="AP71">
+        <v>2.5</v>
+      </c>
+      <c r="AQ71">
+        <v>0.5</v>
+      </c>
+      <c r="AR71">
+        <v>1.88</v>
+      </c>
+      <c r="AS71">
+        <v>1</v>
+      </c>
+      <c r="AT71">
+        <v>2.88</v>
+      </c>
+      <c r="AU71">
+        <v>8</v>
+      </c>
+      <c r="AV71">
+        <v>7</v>
+      </c>
+      <c r="AW71">
+        <v>13</v>
+      </c>
+      <c r="AX71">
+        <v>10</v>
+      </c>
+      <c r="AY71">
+        <v>21</v>
+      </c>
+      <c r="AZ71">
+        <v>17</v>
+      </c>
+      <c r="BA71">
+        <v>8</v>
+      </c>
+      <c r="BB71">
+        <v>6</v>
+      </c>
+      <c r="BC71">
+        <v>14</v>
+      </c>
+      <c r="BD71">
+        <v>1.14</v>
+      </c>
+      <c r="BE71">
+        <v>11.75</v>
+      </c>
+      <c r="BF71">
+        <v>6.45</v>
+      </c>
+      <c r="BG71">
+        <v>1.26</v>
+      </c>
+      <c r="BH71">
+        <v>3.22</v>
+      </c>
+      <c r="BI71">
+        <v>1.52</v>
+      </c>
+      <c r="BJ71">
+        <v>2.45</v>
+      </c>
+      <c r="BK71">
+        <v>2.1</v>
+      </c>
+      <c r="BL71">
+        <v>1.87</v>
+      </c>
+      <c r="BM71">
+        <v>2.43</v>
+      </c>
+      <c r="BN71">
+        <v>1.54</v>
+      </c>
+      <c r="BO71">
+        <v>3.2</v>
+      </c>
+      <c r="BP71">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="159">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -391,6 +391,9 @@
     <t>['62', '90+1']</t>
   </si>
   <si>
+    <t>['12', '36', '45+6']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -485,6 +488,9 @@
   </si>
   <si>
     <t>['33']</t>
+  </si>
+  <si>
+    <t>['25', '86']</t>
   </si>
 </sst>
 </file>
@@ -846,7 +852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP71"/>
+  <dimension ref="A1:BP73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1102,7 +1108,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1308,7 +1314,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1926,7 +1932,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2132,7 +2138,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2338,7 +2344,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2416,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
         <v>1.5</v>
@@ -2750,7 +2756,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -2956,7 +2962,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3243,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="AQ12">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3368,7 +3374,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3574,7 +3580,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3780,7 +3786,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -3986,7 +3992,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4273,7 +4279,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ17">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4476,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ18">
         <v>0.5</v>
@@ -4810,7 +4816,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5016,7 +5022,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5222,7 +5228,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q22">
         <v>1.91</v>
@@ -5634,7 +5640,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5840,7 +5846,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -5918,7 +5924,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
         <v>2</v>
@@ -6745,7 +6751,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ29">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR29">
         <v>0.83</v>
@@ -6870,7 +6876,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7076,7 +7082,7 @@
         <v>89</v>
       </c>
       <c r="P31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7900,7 +7906,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -7981,7 +7987,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ35">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>2.03</v>
@@ -8184,7 +8190,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ36">
         <v>1.75</v>
@@ -8312,7 +8318,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8930,7 +8936,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9008,7 +9014,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ40">
         <v>1.6</v>
@@ -9136,7 +9142,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9548,7 +9554,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9960,7 +9966,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10372,7 +10378,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10784,7 +10790,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -10865,7 +10871,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR49">
         <v>1.04</v>
@@ -11071,7 +11077,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ50">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AR50">
         <v>1.6</v>
@@ -11196,7 +11202,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11402,7 +11408,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11608,7 +11614,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -11686,7 +11692,7 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ53">
         <v>2</v>
@@ -12304,7 +12310,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
         <v>1.25</v>
@@ -12432,7 +12438,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12844,7 +12850,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -13256,7 +13262,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -14286,7 +14292,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14698,7 +14704,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15473,6 +15479,418 @@
       </c>
       <c r="BP71">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:68">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>7729604</v>
+      </c>
+      <c r="C72" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="2">
+        <v>45673.45833333334</v>
+      </c>
+      <c r="F72">
+        <v>8</v>
+      </c>
+      <c r="G72" t="s">
+        <v>76</v>
+      </c>
+      <c r="H72" t="s">
+        <v>70</v>
+      </c>
+      <c r="I72">
+        <v>3</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>4</v>
+      </c>
+      <c r="L72">
+        <v>3</v>
+      </c>
+      <c r="M72">
+        <v>2</v>
+      </c>
+      <c r="N72">
+        <v>5</v>
+      </c>
+      <c r="O72" t="s">
+        <v>125</v>
+      </c>
+      <c r="P72" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q72">
+        <v>1.73</v>
+      </c>
+      <c r="R72">
+        <v>2.25</v>
+      </c>
+      <c r="S72">
+        <v>11</v>
+      </c>
+      <c r="T72">
+        <v>1.51</v>
+      </c>
+      <c r="U72">
+        <v>2.4</v>
+      </c>
+      <c r="V72">
+        <v>3.26</v>
+      </c>
+      <c r="W72">
+        <v>1.31</v>
+      </c>
+      <c r="X72">
+        <v>9.4</v>
+      </c>
+      <c r="Y72">
+        <v>1.04</v>
+      </c>
+      <c r="Z72">
+        <v>1.42</v>
+      </c>
+      <c r="AA72">
+        <v>3.55</v>
+      </c>
+      <c r="AB72">
+        <v>6</v>
+      </c>
+      <c r="AC72">
+        <v>1.01</v>
+      </c>
+      <c r="AD72">
+        <v>8.4</v>
+      </c>
+      <c r="AE72">
+        <v>1.39</v>
+      </c>
+      <c r="AF72">
+        <v>2.85</v>
+      </c>
+      <c r="AG72">
+        <v>2.18</v>
+      </c>
+      <c r="AH72">
+        <v>1.64</v>
+      </c>
+      <c r="AI72">
+        <v>3</v>
+      </c>
+      <c r="AJ72">
+        <v>1.36</v>
+      </c>
+      <c r="AK72">
+        <v>1.08</v>
+      </c>
+      <c r="AL72">
+        <v>1.2</v>
+      </c>
+      <c r="AM72">
+        <v>2.3</v>
+      </c>
+      <c r="AN72">
+        <v>1.75</v>
+      </c>
+      <c r="AO72">
+        <v>0.33</v>
+      </c>
+      <c r="AP72">
+        <v>2</v>
+      </c>
+      <c r="AQ72">
+        <v>0.25</v>
+      </c>
+      <c r="AR72">
+        <v>1.61</v>
+      </c>
+      <c r="AS72">
+        <v>1.09</v>
+      </c>
+      <c r="AT72">
+        <v>2.7</v>
+      </c>
+      <c r="AU72">
+        <v>11</v>
+      </c>
+      <c r="AV72">
+        <v>4</v>
+      </c>
+      <c r="AW72">
+        <v>7</v>
+      </c>
+      <c r="AX72">
+        <v>4</v>
+      </c>
+      <c r="AY72">
+        <v>18</v>
+      </c>
+      <c r="AZ72">
+        <v>8</v>
+      </c>
+      <c r="BA72">
+        <v>1</v>
+      </c>
+      <c r="BB72">
+        <v>5</v>
+      </c>
+      <c r="BC72">
+        <v>6</v>
+      </c>
+      <c r="BD72">
+        <v>1.16</v>
+      </c>
+      <c r="BE72">
+        <v>10.75</v>
+      </c>
+      <c r="BF72">
+        <v>6</v>
+      </c>
+      <c r="BG72">
+        <v>1.28</v>
+      </c>
+      <c r="BH72">
+        <v>3.08</v>
+      </c>
+      <c r="BI72">
+        <v>1.58</v>
+      </c>
+      <c r="BJ72">
+        <v>2.31</v>
+      </c>
+      <c r="BK72">
+        <v>1.99</v>
+      </c>
+      <c r="BL72">
+        <v>1.81</v>
+      </c>
+      <c r="BM72">
+        <v>2.58</v>
+      </c>
+      <c r="BN72">
+        <v>1.48</v>
+      </c>
+      <c r="BO72">
+        <v>3.34</v>
+      </c>
+      <c r="BP72">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:68">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>7729605</v>
+      </c>
+      <c r="C73" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73" s="2">
+        <v>45673.58333333334</v>
+      </c>
+      <c r="F73">
+        <v>8</v>
+      </c>
+      <c r="G73" t="s">
+        <v>86</v>
+      </c>
+      <c r="H73" t="s">
+        <v>74</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>1</v>
+      </c>
+      <c r="O73" t="s">
+        <v>107</v>
+      </c>
+      <c r="P73" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q73">
+        <v>2.5</v>
+      </c>
+      <c r="R73">
+        <v>1.91</v>
+      </c>
+      <c r="S73">
+        <v>5</v>
+      </c>
+      <c r="T73">
+        <v>1.56</v>
+      </c>
+      <c r="U73">
+        <v>2.3</v>
+      </c>
+      <c r="V73">
+        <v>3.32</v>
+      </c>
+      <c r="W73">
+        <v>1.3</v>
+      </c>
+      <c r="X73">
+        <v>8.4</v>
+      </c>
+      <c r="Y73">
+        <v>1.05</v>
+      </c>
+      <c r="Z73">
+        <v>1.8</v>
+      </c>
+      <c r="AA73">
+        <v>3.1</v>
+      </c>
+      <c r="AB73">
+        <v>4.5</v>
+      </c>
+      <c r="AC73">
+        <v>1.07</v>
+      </c>
+      <c r="AD73">
+        <v>5.95</v>
+      </c>
+      <c r="AE73">
+        <v>1.5</v>
+      </c>
+      <c r="AF73">
+        <v>2.4</v>
+      </c>
+      <c r="AG73">
+        <v>2.5</v>
+      </c>
+      <c r="AH73">
+        <v>1.5</v>
+      </c>
+      <c r="AI73">
+        <v>2.25</v>
+      </c>
+      <c r="AJ73">
+        <v>1.57</v>
+      </c>
+      <c r="AK73">
+        <v>1.15</v>
+      </c>
+      <c r="AL73">
+        <v>1.28</v>
+      </c>
+      <c r="AM73">
+        <v>1.85</v>
+      </c>
+      <c r="AN73">
+        <v>1.33</v>
+      </c>
+      <c r="AO73">
+        <v>1.33</v>
+      </c>
+      <c r="AP73">
+        <v>1.75</v>
+      </c>
+      <c r="AQ73">
+        <v>1</v>
+      </c>
+      <c r="AR73">
+        <v>1.04</v>
+      </c>
+      <c r="AS73">
+        <v>0.93</v>
+      </c>
+      <c r="AT73">
+        <v>1.97</v>
+      </c>
+      <c r="AU73">
+        <v>2</v>
+      </c>
+      <c r="AV73">
+        <v>3</v>
+      </c>
+      <c r="AW73">
+        <v>4</v>
+      </c>
+      <c r="AX73">
+        <v>10</v>
+      </c>
+      <c r="AY73">
+        <v>6</v>
+      </c>
+      <c r="AZ73">
+        <v>13</v>
+      </c>
+      <c r="BA73">
+        <v>6</v>
+      </c>
+      <c r="BB73">
+        <v>4</v>
+      </c>
+      <c r="BC73">
+        <v>10</v>
+      </c>
+      <c r="BD73">
+        <v>1.35</v>
+      </c>
+      <c r="BE73">
+        <v>7.2</v>
+      </c>
+      <c r="BF73">
+        <v>4.2</v>
+      </c>
+      <c r="BG73">
+        <v>1.42</v>
+      </c>
+      <c r="BH73">
+        <v>2.62</v>
+      </c>
+      <c r="BI73">
+        <v>1.72</v>
+      </c>
+      <c r="BJ73">
+        <v>2.09</v>
+      </c>
+      <c r="BK73">
+        <v>2.2</v>
+      </c>
+      <c r="BL73">
+        <v>1.65</v>
+      </c>
+      <c r="BM73">
+        <v>2.7</v>
+      </c>
+      <c r="BN73">
+        <v>1.4</v>
+      </c>
+      <c r="BO73">
+        <v>3.6</v>
+      </c>
+      <c r="BP73">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
@@ -15627,16 +15627,16 @@
         <v>4</v>
       </c>
       <c r="AW72">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY72">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ72">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA72">
         <v>1</v>
@@ -15827,22 +15827,22 @@
         <v>1.97</v>
       </c>
       <c r="AU73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW73">
         <v>4</v>
       </c>
       <c r="AX73">
+        <v>7</v>
+      </c>
+      <c r="AY73">
         <v>10</v>
       </c>
-      <c r="AY73">
-        <v>6</v>
-      </c>
       <c r="AZ73">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA73">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="163">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -394,6 +394,9 @@
     <t>['12', '36', '45+6']</t>
   </si>
   <si>
+    <t>['12']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -491,6 +494,15 @@
   </si>
   <si>
     <t>['25', '86']</t>
+  </si>
+  <si>
+    <t>['35', '59']</t>
+  </si>
+  <si>
+    <t>['82']</t>
+  </si>
+  <si>
+    <t>['61']</t>
   </si>
 </sst>
 </file>
@@ -852,7 +864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP73"/>
+  <dimension ref="A1:BP77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1108,7 +1120,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1189,7 +1201,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1314,7 +1326,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1598,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ4">
         <v>2</v>
@@ -1932,7 +1944,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2138,7 +2150,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2344,7 +2356,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2425,7 +2437,7 @@
         <v>2</v>
       </c>
       <c r="AQ8">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2628,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ9">
         <v>1.75</v>
@@ -2756,7 +2768,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -2962,7 +2974,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3040,10 +3052,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3249,7 +3261,7 @@
         <v>1</v>
       </c>
       <c r="AQ12">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3374,7 +3386,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3580,7 +3592,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3786,7 +3798,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -3992,7 +4004,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4070,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ16">
         <v>1.75</v>
@@ -4816,7 +4828,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5022,7 +5034,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5103,7 +5115,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ21">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR21">
         <v>1.79</v>
@@ -5228,7 +5240,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q22">
         <v>1.91</v>
@@ -5515,7 +5527,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -5640,7 +5652,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5718,7 +5730,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ24">
         <v>1.75</v>
@@ -5846,7 +5858,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -6130,7 +6142,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ26">
         <v>1.25</v>
@@ -6751,7 +6763,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ29">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR29">
         <v>0.83</v>
@@ -6876,7 +6888,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -7082,7 +7094,7 @@
         <v>89</v>
       </c>
       <c r="P31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7163,7 +7175,7 @@
         <v>1</v>
       </c>
       <c r="AQ31">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR31">
         <v>1.06</v>
@@ -7778,7 +7790,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ34">
         <v>0.25</v>
@@ -7906,7 +7918,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -8318,7 +8330,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8396,7 +8408,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ37">
         <v>2.33</v>
@@ -8936,7 +8948,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9142,7 +9154,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9223,7 +9235,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ41">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR41">
         <v>1.57</v>
@@ -9426,7 +9438,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ42">
         <v>0.6</v>
@@ -9554,7 +9566,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9838,7 +9850,7 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ44">
         <v>1.25</v>
@@ -9966,7 +9978,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10044,7 +10056,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ45">
         <v>1.75</v>
@@ -10378,7 +10390,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10790,7 +10802,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -10868,10 +10880,10 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ49">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR49">
         <v>1.04</v>
@@ -11202,7 +11214,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11408,7 +11420,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11614,7 +11626,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -12107,7 +12119,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ55">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AR55">
         <v>0.74</v>
@@ -12438,7 +12450,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12516,7 +12528,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ57">
         <v>1.75</v>
@@ -12722,7 +12734,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ58">
         <v>2</v>
@@ -12850,7 +12862,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -12931,7 +12943,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ59">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR59">
         <v>1.58</v>
@@ -13262,7 +13274,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13752,10 +13764,10 @@
         <v>1</v>
       </c>
       <c r="AP63">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AQ63">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR63">
         <v>1.51</v>
@@ -13961,7 +13973,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ64">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR64">
         <v>2.21</v>
@@ -14292,7 +14304,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14704,7 +14716,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15528,7 +15540,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -15609,7 +15621,7 @@
         <v>2</v>
       </c>
       <c r="AQ72">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR72">
         <v>1.61</v>
@@ -15891,6 +15903,830 @@
       </c>
       <c r="BP73">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:68">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>7729606</v>
+      </c>
+      <c r="C74" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="2">
+        <v>45678.45833333334</v>
+      </c>
+      <c r="F74">
+        <v>9</v>
+      </c>
+      <c r="G74" t="s">
+        <v>72</v>
+      </c>
+      <c r="H74" t="s">
+        <v>85</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="K74">
+        <v>2</v>
+      </c>
+      <c r="L74">
+        <v>1</v>
+      </c>
+      <c r="M74">
+        <v>2</v>
+      </c>
+      <c r="N74">
+        <v>3</v>
+      </c>
+      <c r="O74" t="s">
+        <v>126</v>
+      </c>
+      <c r="P74" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q74">
+        <v>3.4</v>
+      </c>
+      <c r="R74">
+        <v>1.8</v>
+      </c>
+      <c r="S74">
+        <v>4</v>
+      </c>
+      <c r="T74">
+        <v>1.69</v>
+      </c>
+      <c r="U74">
+        <v>2.07</v>
+      </c>
+      <c r="V74">
+        <v>3.7</v>
+      </c>
+      <c r="W74">
+        <v>1.25</v>
+      </c>
+      <c r="X74">
+        <v>9.9</v>
+      </c>
+      <c r="Y74">
+        <v>1.03</v>
+      </c>
+      <c r="Z74">
+        <v>3.8</v>
+      </c>
+      <c r="AA74">
+        <v>2.62</v>
+      </c>
+      <c r="AB74">
+        <v>2.1</v>
+      </c>
+      <c r="AC74">
+        <v>1.13</v>
+      </c>
+      <c r="AD74">
+        <v>6</v>
+      </c>
+      <c r="AE74">
+        <v>1.57</v>
+      </c>
+      <c r="AF74">
+        <v>2.15</v>
+      </c>
+      <c r="AG74">
+        <v>2.81</v>
+      </c>
+      <c r="AH74">
+        <v>1.38</v>
+      </c>
+      <c r="AI74">
+        <v>2.5</v>
+      </c>
+      <c r="AJ74">
+        <v>1.5</v>
+      </c>
+      <c r="AK74">
+        <v>1.6</v>
+      </c>
+      <c r="AL74">
+        <v>1.37</v>
+      </c>
+      <c r="AM74">
+        <v>1.21</v>
+      </c>
+      <c r="AN74">
+        <v>1</v>
+      </c>
+      <c r="AO74">
+        <v>1.5</v>
+      </c>
+      <c r="AP74">
+        <v>0.8</v>
+      </c>
+      <c r="AQ74">
+        <v>1.8</v>
+      </c>
+      <c r="AR74">
+        <v>1.35</v>
+      </c>
+      <c r="AS74">
+        <v>1.12</v>
+      </c>
+      <c r="AT74">
+        <v>2.47</v>
+      </c>
+      <c r="AU74">
+        <v>2</v>
+      </c>
+      <c r="AV74">
+        <v>3</v>
+      </c>
+      <c r="AW74">
+        <v>4</v>
+      </c>
+      <c r="AX74">
+        <v>2</v>
+      </c>
+      <c r="AY74">
+        <v>6</v>
+      </c>
+      <c r="AZ74">
+        <v>5</v>
+      </c>
+      <c r="BA74">
+        <v>7</v>
+      </c>
+      <c r="BB74">
+        <v>4</v>
+      </c>
+      <c r="BC74">
+        <v>11</v>
+      </c>
+      <c r="BD74">
+        <v>2.18</v>
+      </c>
+      <c r="BE74">
+        <v>6.2</v>
+      </c>
+      <c r="BF74">
+        <v>2.01</v>
+      </c>
+      <c r="BG74">
+        <v>1.26</v>
+      </c>
+      <c r="BH74">
+        <v>3.22</v>
+      </c>
+      <c r="BI74">
+        <v>1.59</v>
+      </c>
+      <c r="BJ74">
+        <v>2.31</v>
+      </c>
+      <c r="BK74">
+        <v>2.38</v>
+      </c>
+      <c r="BL74">
+        <v>1.85</v>
+      </c>
+      <c r="BM74">
+        <v>2.44</v>
+      </c>
+      <c r="BN74">
+        <v>1.53</v>
+      </c>
+      <c r="BO74">
+        <v>3.28</v>
+      </c>
+      <c r="BP74">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:68">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>7729607</v>
+      </c>
+      <c r="C75" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="2">
+        <v>45678.45833333334</v>
+      </c>
+      <c r="F75">
+        <v>9</v>
+      </c>
+      <c r="G75" t="s">
+        <v>79</v>
+      </c>
+      <c r="H75" t="s">
+        <v>70</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
+      <c r="O75" t="s">
+        <v>89</v>
+      </c>
+      <c r="P75" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q75">
+        <v>2.88</v>
+      </c>
+      <c r="R75">
+        <v>1.8</v>
+      </c>
+      <c r="S75">
+        <v>5</v>
+      </c>
+      <c r="T75">
+        <v>1.73</v>
+      </c>
+      <c r="U75">
+        <v>2.02</v>
+      </c>
+      <c r="V75">
+        <v>4</v>
+      </c>
+      <c r="W75">
+        <v>1.2</v>
+      </c>
+      <c r="X75">
+        <v>10.5</v>
+      </c>
+      <c r="Y75">
+        <v>1.03</v>
+      </c>
+      <c r="Z75">
+        <v>2.1</v>
+      </c>
+      <c r="AA75">
+        <v>2.5</v>
+      </c>
+      <c r="AB75">
+        <v>4.2</v>
+      </c>
+      <c r="AC75">
+        <v>1.13</v>
+      </c>
+      <c r="AD75">
+        <v>6</v>
+      </c>
+      <c r="AE75">
+        <v>1.61</v>
+      </c>
+      <c r="AF75">
+        <v>2.05</v>
+      </c>
+      <c r="AG75">
+        <v>2.99</v>
+      </c>
+      <c r="AH75">
+        <v>1.34</v>
+      </c>
+      <c r="AI75">
+        <v>2.5</v>
+      </c>
+      <c r="AJ75">
+        <v>1.5</v>
+      </c>
+      <c r="AK75">
+        <v>1.19</v>
+      </c>
+      <c r="AL75">
+        <v>1.38</v>
+      </c>
+      <c r="AM75">
+        <v>1.62</v>
+      </c>
+      <c r="AN75">
+        <v>0.25</v>
+      </c>
+      <c r="AO75">
+        <v>0.25</v>
+      </c>
+      <c r="AP75">
+        <v>0.2</v>
+      </c>
+      <c r="AQ75">
+        <v>0.8</v>
+      </c>
+      <c r="AR75">
+        <v>1.53</v>
+      </c>
+      <c r="AS75">
+        <v>1.06</v>
+      </c>
+      <c r="AT75">
+        <v>2.59</v>
+      </c>
+      <c r="AU75">
+        <v>4</v>
+      </c>
+      <c r="AV75">
+        <v>4</v>
+      </c>
+      <c r="AW75">
+        <v>5</v>
+      </c>
+      <c r="AX75">
+        <v>2</v>
+      </c>
+      <c r="AY75">
+        <v>9</v>
+      </c>
+      <c r="AZ75">
+        <v>6</v>
+      </c>
+      <c r="BA75">
+        <v>11</v>
+      </c>
+      <c r="BB75">
+        <v>2</v>
+      </c>
+      <c r="BC75">
+        <v>13</v>
+      </c>
+      <c r="BD75">
+        <v>1.58</v>
+      </c>
+      <c r="BE75">
+        <v>6.4</v>
+      </c>
+      <c r="BF75">
+        <v>3.04</v>
+      </c>
+      <c r="BG75">
+        <v>1.37</v>
+      </c>
+      <c r="BH75">
+        <v>2.66</v>
+      </c>
+      <c r="BI75">
+        <v>1.76</v>
+      </c>
+      <c r="BJ75">
+        <v>2.03</v>
+      </c>
+      <c r="BK75">
+        <v>2.25</v>
+      </c>
+      <c r="BL75">
+        <v>1.63</v>
+      </c>
+      <c r="BM75">
+        <v>2.92</v>
+      </c>
+      <c r="BN75">
+        <v>1.31</v>
+      </c>
+      <c r="BO75">
+        <v>4.1</v>
+      </c>
+      <c r="BP75">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="76" spans="1:68">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>7729608</v>
+      </c>
+      <c r="C76" t="s">
+        <v>68</v>
+      </c>
+      <c r="D76" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76" s="2">
+        <v>45678.58333333334</v>
+      </c>
+      <c r="F76">
+        <v>9</v>
+      </c>
+      <c r="G76" t="s">
+        <v>84</v>
+      </c>
+      <c r="H76" t="s">
+        <v>71</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>1</v>
+      </c>
+      <c r="N76">
+        <v>1</v>
+      </c>
+      <c r="O76" t="s">
+        <v>89</v>
+      </c>
+      <c r="P76" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q76">
+        <v>3.4</v>
+      </c>
+      <c r="R76">
+        <v>1.67</v>
+      </c>
+      <c r="S76">
+        <v>4.75</v>
+      </c>
+      <c r="T76">
+        <v>1.78</v>
+      </c>
+      <c r="U76">
+        <v>1.95</v>
+      </c>
+      <c r="V76">
+        <v>4</v>
+      </c>
+      <c r="W76">
+        <v>1.22</v>
+      </c>
+      <c r="X76">
+        <v>11</v>
+      </c>
+      <c r="Y76">
+        <v>1.02</v>
+      </c>
+      <c r="Z76">
+        <v>2.4</v>
+      </c>
+      <c r="AA76">
+        <v>2.4</v>
+      </c>
+      <c r="AB76">
+        <v>3.8</v>
+      </c>
+      <c r="AC76">
+        <v>1.13</v>
+      </c>
+      <c r="AD76">
+        <v>6</v>
+      </c>
+      <c r="AE76">
+        <v>1.65</v>
+      </c>
+      <c r="AF76">
+        <v>2.05</v>
+      </c>
+      <c r="AG76">
+        <v>4</v>
+      </c>
+      <c r="AH76">
+        <v>1.22</v>
+      </c>
+      <c r="AI76">
+        <v>3</v>
+      </c>
+      <c r="AJ76">
+        <v>1.36</v>
+      </c>
+      <c r="AK76">
+        <v>1.27</v>
+      </c>
+      <c r="AL76">
+        <v>1.4</v>
+      </c>
+      <c r="AM76">
+        <v>1.47</v>
+      </c>
+      <c r="AN76">
+        <v>1.33</v>
+      </c>
+      <c r="AO76">
+        <v>2</v>
+      </c>
+      <c r="AP76">
+        <v>1</v>
+      </c>
+      <c r="AQ76">
+        <v>2.25</v>
+      </c>
+      <c r="AR76">
+        <v>0.77</v>
+      </c>
+      <c r="AS76">
+        <v>1.14</v>
+      </c>
+      <c r="AT76">
+        <v>1.91</v>
+      </c>
+      <c r="AU76">
+        <v>2</v>
+      </c>
+      <c r="AV76">
+        <v>4</v>
+      </c>
+      <c r="AW76">
+        <v>3</v>
+      </c>
+      <c r="AX76">
+        <v>7</v>
+      </c>
+      <c r="AY76">
+        <v>5</v>
+      </c>
+      <c r="AZ76">
+        <v>11</v>
+      </c>
+      <c r="BA76">
+        <v>5</v>
+      </c>
+      <c r="BB76">
+        <v>2</v>
+      </c>
+      <c r="BC76">
+        <v>7</v>
+      </c>
+      <c r="BD76">
+        <v>1.61</v>
+      </c>
+      <c r="BE76">
+        <v>6.4</v>
+      </c>
+      <c r="BF76">
+        <v>2.94</v>
+      </c>
+      <c r="BG76">
+        <v>1.33</v>
+      </c>
+      <c r="BH76">
+        <v>2.83</v>
+      </c>
+      <c r="BI76">
+        <v>1.7</v>
+      </c>
+      <c r="BJ76">
+        <v>2.12</v>
+      </c>
+      <c r="BK76">
+        <v>2.12</v>
+      </c>
+      <c r="BL76">
+        <v>1.7</v>
+      </c>
+      <c r="BM76">
+        <v>2.74</v>
+      </c>
+      <c r="BN76">
+        <v>1.35</v>
+      </c>
+      <c r="BO76">
+        <v>3.85</v>
+      </c>
+      <c r="BP76">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:68">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>7729609</v>
+      </c>
+      <c r="C77" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77" s="2">
+        <v>45678.58333333334</v>
+      </c>
+      <c r="F77">
+        <v>9</v>
+      </c>
+      <c r="G77" t="s">
+        <v>77</v>
+      </c>
+      <c r="H77" t="s">
+        <v>82</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>1</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>1</v>
+      </c>
+      <c r="O77" t="s">
+        <v>104</v>
+      </c>
+      <c r="P77" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q77">
+        <v>4</v>
+      </c>
+      <c r="R77">
+        <v>1.83</v>
+      </c>
+      <c r="S77">
+        <v>3</v>
+      </c>
+      <c r="T77">
+        <v>1.65</v>
+      </c>
+      <c r="U77">
+        <v>2.13</v>
+      </c>
+      <c r="V77">
+        <v>3.5</v>
+      </c>
+      <c r="W77">
+        <v>1.28</v>
+      </c>
+      <c r="X77">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y77">
+        <v>1.04</v>
+      </c>
+      <c r="Z77">
+        <v>3.4</v>
+      </c>
+      <c r="AA77">
+        <v>2.9</v>
+      </c>
+      <c r="AB77">
+        <v>2.2</v>
+      </c>
+      <c r="AC77">
+        <v>1.1</v>
+      </c>
+      <c r="AD77">
+        <v>6.5</v>
+      </c>
+      <c r="AE77">
+        <v>1.53</v>
+      </c>
+      <c r="AF77">
+        <v>2.25</v>
+      </c>
+      <c r="AG77">
+        <v>2.63</v>
+      </c>
+      <c r="AH77">
+        <v>1.44</v>
+      </c>
+      <c r="AI77">
+        <v>2.25</v>
+      </c>
+      <c r="AJ77">
+        <v>1.57</v>
+      </c>
+      <c r="AK77">
+        <v>1.45</v>
+      </c>
+      <c r="AL77">
+        <v>1.35</v>
+      </c>
+      <c r="AM77">
+        <v>1.33</v>
+      </c>
+      <c r="AN77">
+        <v>1.5</v>
+      </c>
+      <c r="AO77">
+        <v>1</v>
+      </c>
+      <c r="AP77">
+        <v>1.8</v>
+      </c>
+      <c r="AQ77">
+        <v>0.8</v>
+      </c>
+      <c r="AR77">
+        <v>1.1</v>
+      </c>
+      <c r="AS77">
+        <v>1.36</v>
+      </c>
+      <c r="AT77">
+        <v>2.46</v>
+      </c>
+      <c r="AU77">
+        <v>3</v>
+      </c>
+      <c r="AV77">
+        <v>5</v>
+      </c>
+      <c r="AW77">
+        <v>3</v>
+      </c>
+      <c r="AX77">
+        <v>6</v>
+      </c>
+      <c r="AY77">
+        <v>6</v>
+      </c>
+      <c r="AZ77">
+        <v>11</v>
+      </c>
+      <c r="BA77">
+        <v>3</v>
+      </c>
+      <c r="BB77">
+        <v>2</v>
+      </c>
+      <c r="BC77">
+        <v>5</v>
+      </c>
+      <c r="BD77">
+        <v>2.32</v>
+      </c>
+      <c r="BE77">
+        <v>6.25</v>
+      </c>
+      <c r="BF77">
+        <v>1.9</v>
+      </c>
+      <c r="BG77">
+        <v>1.27</v>
+      </c>
+      <c r="BH77">
+        <v>3.14</v>
+      </c>
+      <c r="BI77">
+        <v>1.59</v>
+      </c>
+      <c r="BJ77">
+        <v>2.31</v>
+      </c>
+      <c r="BK77">
+        <v>1.98</v>
+      </c>
+      <c r="BL77">
+        <v>1.82</v>
+      </c>
+      <c r="BM77">
+        <v>2.5</v>
+      </c>
+      <c r="BN77">
+        <v>1.5</v>
+      </c>
+      <c r="BO77">
+        <v>3.34</v>
+      </c>
+      <c r="BP77">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="169">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -397,6 +397,15 @@
     <t>['12']</t>
   </si>
   <si>
+    <t>['22']</t>
+  </si>
+  <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['17', '37']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -503,6 +512,15 @@
   </si>
   <si>
     <t>['61']</t>
+  </si>
+  <si>
+    <t>['45+11']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
+    <t>['80']</t>
   </si>
 </sst>
 </file>
@@ -864,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP77"/>
+  <dimension ref="A1:BP81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1120,7 +1138,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1326,7 +1344,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1407,7 +1425,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ3">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1944,7 +1962,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2022,10 +2040,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ6">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2150,7 +2168,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2356,7 +2374,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2768,7 +2786,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -2974,7 +2992,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3386,7 +3404,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3464,10 +3482,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3592,7 +3610,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3798,7 +3816,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -3876,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ15">
         <v>0.5</v>
@@ -4004,7 +4022,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4085,7 +4103,7 @@
         <v>1</v>
       </c>
       <c r="AQ16">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4700,7 +4718,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
         <v>0.25</v>
@@ -4828,7 +4846,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -4906,7 +4924,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ20">
         <v>0.6</v>
@@ -5034,7 +5052,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5240,7 +5258,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q22">
         <v>1.91</v>
@@ -5321,7 +5339,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ22">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR22">
         <v>1.96</v>
@@ -5652,7 +5670,7 @@
         <v>89</v>
       </c>
       <c r="P24" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="Q24">
         <v>3.5</v>
@@ -5858,7 +5876,7 @@
         <v>89</v>
       </c>
       <c r="P25" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="Q25">
         <v>3</v>
@@ -5939,7 +5957,7 @@
         <v>2</v>
       </c>
       <c r="AQ25">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR25">
         <v>1.36</v>
@@ -6760,7 +6778,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ29">
         <v>0.8</v>
@@ -6888,7 +6906,7 @@
         <v>103</v>
       </c>
       <c r="P30" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q30">
         <v>3</v>
@@ -6966,7 +6984,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
         <v>0.5</v>
@@ -7094,7 +7112,7 @@
         <v>89</v>
       </c>
       <c r="P31" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7381,7 +7399,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ32">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR32">
         <v>1.11</v>
@@ -7918,7 +7936,7 @@
         <v>105</v>
       </c>
       <c r="P35" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q35">
         <v>3.1</v>
@@ -7996,7 +8014,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8205,7 +8223,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ36">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR36">
         <v>1.03</v>
@@ -8330,7 +8348,7 @@
         <v>89</v>
       </c>
       <c r="P37" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q37">
         <v>4.5</v>
@@ -8617,7 +8635,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ38">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR38">
         <v>0.8100000000000001</v>
@@ -8948,7 +8966,7 @@
         <v>107</v>
       </c>
       <c r="P40" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -9154,7 +9172,7 @@
         <v>89</v>
       </c>
       <c r="P41" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q41">
         <v>3.4</v>
@@ -9566,7 +9584,7 @@
         <v>109</v>
       </c>
       <c r="P43" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9644,7 +9662,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ43">
         <v>2</v>
@@ -9853,7 +9871,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ44">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR44">
         <v>1.55</v>
@@ -9978,7 +9996,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10059,7 +10077,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ45">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR45">
         <v>1.27</v>
@@ -10262,7 +10280,7 @@
         <v>0.33</v>
       </c>
       <c r="AP46">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ46">
         <v>0.6</v>
@@ -10390,7 +10408,7 @@
         <v>111</v>
       </c>
       <c r="P47" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q47">
         <v>4.75</v>
@@ -10802,7 +10820,7 @@
         <v>112</v>
       </c>
       <c r="P49" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q49">
         <v>2.6</v>
@@ -11214,7 +11232,7 @@
         <v>114</v>
       </c>
       <c r="P51" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q51">
         <v>3.6</v>
@@ -11420,7 +11438,7 @@
         <v>115</v>
       </c>
       <c r="P52" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11626,7 +11644,7 @@
         <v>89</v>
       </c>
       <c r="P53" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q53">
         <v>5</v>
@@ -11707,7 +11725,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ53">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR53">
         <v>0.97</v>
@@ -11910,7 +11928,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ54">
         <v>0.5</v>
@@ -12325,7 +12343,7 @@
         <v>2</v>
       </c>
       <c r="AQ56">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR56">
         <v>1.48</v>
@@ -12450,7 +12468,7 @@
         <v>89</v>
       </c>
       <c r="P57" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12531,7 +12549,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ57">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR57">
         <v>1.49</v>
@@ -12737,7 +12755,7 @@
         <v>1</v>
       </c>
       <c r="AQ58">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AR58">
         <v>0.89</v>
@@ -12862,7 +12880,7 @@
         <v>119</v>
       </c>
       <c r="P59" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q59">
         <v>3.75</v>
@@ -12940,7 +12958,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ59">
         <v>0.8</v>
@@ -13146,7 +13164,7 @@
         <v>1.33</v>
       </c>
       <c r="AP60">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ60">
         <v>1.25</v>
@@ -13274,7 +13292,7 @@
         <v>106</v>
       </c>
       <c r="P61" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q61">
         <v>3.6</v>
@@ -13352,10 +13370,10 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ61">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AR61">
         <v>1.52</v>
@@ -14176,7 +14194,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AQ65">
         <v>0.6</v>
@@ -14304,7 +14322,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -14716,7 +14734,7 @@
         <v>89</v>
       </c>
       <c r="P68" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15540,7 +15558,7 @@
         <v>125</v>
       </c>
       <c r="P72" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q72">
         <v>1.73</v>
@@ -15952,7 +15970,7 @@
         <v>126</v>
       </c>
       <c r="P74" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
@@ -16158,7 +16176,7 @@
         <v>89</v>
       </c>
       <c r="P75" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16364,7 +16382,7 @@
         <v>89</v>
       </c>
       <c r="P76" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -16727,6 +16745,830 @@
       </c>
       <c r="BP77">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="78" spans="1:68">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>7729610</v>
+      </c>
+      <c r="C78" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" s="2">
+        <v>45679.45833333334</v>
+      </c>
+      <c r="F78">
+        <v>9</v>
+      </c>
+      <c r="G78" t="s">
+        <v>74</v>
+      </c>
+      <c r="H78" t="s">
+        <v>78</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78">
+        <v>2</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+      <c r="N78">
+        <v>2</v>
+      </c>
+      <c r="O78" t="s">
+        <v>127</v>
+      </c>
+      <c r="P78" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q78">
+        <v>6</v>
+      </c>
+      <c r="R78">
+        <v>2.1</v>
+      </c>
+      <c r="S78">
+        <v>2.2</v>
+      </c>
+      <c r="T78">
+        <v>1.38</v>
+      </c>
+      <c r="U78">
+        <v>2.96</v>
+      </c>
+      <c r="V78">
+        <v>2.65</v>
+      </c>
+      <c r="W78">
+        <v>1.42</v>
+      </c>
+      <c r="X78">
+        <v>7.1</v>
+      </c>
+      <c r="Y78">
+        <v>1.08</v>
+      </c>
+      <c r="Z78">
+        <v>6.7</v>
+      </c>
+      <c r="AA78">
+        <v>4.3</v>
+      </c>
+      <c r="AB78">
+        <v>1.44</v>
+      </c>
+      <c r="AC78">
+        <v>1.05</v>
+      </c>
+      <c r="AD78">
+        <v>10</v>
+      </c>
+      <c r="AE78">
+        <v>1.29</v>
+      </c>
+      <c r="AF78">
+        <v>3.5</v>
+      </c>
+      <c r="AG78">
+        <v>1.85</v>
+      </c>
+      <c r="AH78">
+        <v>1.8</v>
+      </c>
+      <c r="AI78">
+        <v>2.2</v>
+      </c>
+      <c r="AJ78">
+        <v>1.62</v>
+      </c>
+      <c r="AK78">
+        <v>2.42</v>
+      </c>
+      <c r="AL78">
+        <v>1.18</v>
+      </c>
+      <c r="AM78">
+        <v>1.08</v>
+      </c>
+      <c r="AN78">
+        <v>1.5</v>
+      </c>
+      <c r="AO78">
+        <v>2</v>
+      </c>
+      <c r="AP78">
+        <v>1.4</v>
+      </c>
+      <c r="AQ78">
+        <v>1.8</v>
+      </c>
+      <c r="AR78">
+        <v>1.46</v>
+      </c>
+      <c r="AS78">
+        <v>1.27</v>
+      </c>
+      <c r="AT78">
+        <v>2.73</v>
+      </c>
+      <c r="AU78">
+        <v>4</v>
+      </c>
+      <c r="AV78">
+        <v>5</v>
+      </c>
+      <c r="AW78">
+        <v>8</v>
+      </c>
+      <c r="AX78">
+        <v>14</v>
+      </c>
+      <c r="AY78">
+        <v>12</v>
+      </c>
+      <c r="AZ78">
+        <v>19</v>
+      </c>
+      <c r="BA78">
+        <v>0</v>
+      </c>
+      <c r="BB78">
+        <v>7</v>
+      </c>
+      <c r="BC78">
+        <v>7</v>
+      </c>
+      <c r="BD78">
+        <v>3.7</v>
+      </c>
+      <c r="BE78">
+        <v>8.9</v>
+      </c>
+      <c r="BF78">
+        <v>1.36</v>
+      </c>
+      <c r="BG78">
+        <v>1.31</v>
+      </c>
+      <c r="BH78">
+        <v>2.92</v>
+      </c>
+      <c r="BI78">
+        <v>1.67</v>
+      </c>
+      <c r="BJ78">
+        <v>2.19</v>
+      </c>
+      <c r="BK78">
+        <v>2.06</v>
+      </c>
+      <c r="BL78">
+        <v>1.75</v>
+      </c>
+      <c r="BM78">
+        <v>2.62</v>
+      </c>
+      <c r="BN78">
+        <v>1.38</v>
+      </c>
+      <c r="BO78">
+        <v>3.68</v>
+      </c>
+      <c r="BP78">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:68">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>7729611</v>
+      </c>
+      <c r="C79" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="2">
+        <v>45679.58333333334</v>
+      </c>
+      <c r="F79">
+        <v>9</v>
+      </c>
+      <c r="G79" t="s">
+        <v>87</v>
+      </c>
+      <c r="H79" t="s">
+        <v>80</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+      <c r="N79">
+        <v>2</v>
+      </c>
+      <c r="O79" t="s">
+        <v>128</v>
+      </c>
+      <c r="P79" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q79">
+        <v>2.3</v>
+      </c>
+      <c r="R79">
+        <v>2</v>
+      </c>
+      <c r="S79">
+        <v>5.5</v>
+      </c>
+      <c r="T79">
+        <v>1.56</v>
+      </c>
+      <c r="U79">
+        <v>2.31</v>
+      </c>
+      <c r="V79">
+        <v>3.4</v>
+      </c>
+      <c r="W79">
+        <v>1.29</v>
+      </c>
+      <c r="X79">
+        <v>8.9</v>
+      </c>
+      <c r="Y79">
+        <v>1.05</v>
+      </c>
+      <c r="Z79">
+        <v>1.65</v>
+      </c>
+      <c r="AA79">
+        <v>3.4</v>
+      </c>
+      <c r="AB79">
+        <v>5.25</v>
+      </c>
+      <c r="AC79">
+        <v>1.07</v>
+      </c>
+      <c r="AD79">
+        <v>7</v>
+      </c>
+      <c r="AE79">
+        <v>1.5</v>
+      </c>
+      <c r="AF79">
+        <v>2.4</v>
+      </c>
+      <c r="AG79">
+        <v>2.2</v>
+      </c>
+      <c r="AH79">
+        <v>1.65</v>
+      </c>
+      <c r="AI79">
+        <v>2.25</v>
+      </c>
+      <c r="AJ79">
+        <v>1.57</v>
+      </c>
+      <c r="AK79">
+        <v>1.13</v>
+      </c>
+      <c r="AL79">
+        <v>1.28</v>
+      </c>
+      <c r="AM79">
+        <v>1.91</v>
+      </c>
+      <c r="AN79">
+        <v>2.33</v>
+      </c>
+      <c r="AO79">
+        <v>1.25</v>
+      </c>
+      <c r="AP79">
+        <v>2</v>
+      </c>
+      <c r="AQ79">
+        <v>1.2</v>
+      </c>
+      <c r="AR79">
+        <v>1.49</v>
+      </c>
+      <c r="AS79">
+        <v>0.87</v>
+      </c>
+      <c r="AT79">
+        <v>2.36</v>
+      </c>
+      <c r="AU79">
+        <v>6</v>
+      </c>
+      <c r="AV79">
+        <v>3</v>
+      </c>
+      <c r="AW79">
+        <v>8</v>
+      </c>
+      <c r="AX79">
+        <v>4</v>
+      </c>
+      <c r="AY79">
+        <v>14</v>
+      </c>
+      <c r="AZ79">
+        <v>7</v>
+      </c>
+      <c r="BA79">
+        <v>12</v>
+      </c>
+      <c r="BB79">
+        <v>0</v>
+      </c>
+      <c r="BC79">
+        <v>12</v>
+      </c>
+      <c r="BD79">
+        <v>1.37</v>
+      </c>
+      <c r="BE79">
+        <v>8</v>
+      </c>
+      <c r="BF79">
+        <v>4.26</v>
+      </c>
+      <c r="BG79">
+        <v>1.38</v>
+      </c>
+      <c r="BH79">
+        <v>2.8</v>
+      </c>
+      <c r="BI79">
+        <v>1.65</v>
+      </c>
+      <c r="BJ79">
+        <v>2.22</v>
+      </c>
+      <c r="BK79">
+        <v>2.07</v>
+      </c>
+      <c r="BL79">
+        <v>1.74</v>
+      </c>
+      <c r="BM79">
+        <v>2.6</v>
+      </c>
+      <c r="BN79">
+        <v>1.44</v>
+      </c>
+      <c r="BO79">
+        <v>3.4</v>
+      </c>
+      <c r="BP79">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:68">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7729612</v>
+      </c>
+      <c r="C80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45679.58333333334</v>
+      </c>
+      <c r="F80">
+        <v>9</v>
+      </c>
+      <c r="G80" t="s">
+        <v>81</v>
+      </c>
+      <c r="H80" t="s">
+        <v>75</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>1</v>
+      </c>
+      <c r="N80">
+        <v>1</v>
+      </c>
+      <c r="O80" t="s">
+        <v>89</v>
+      </c>
+      <c r="P80" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q80">
+        <v>4.33</v>
+      </c>
+      <c r="R80">
+        <v>1.83</v>
+      </c>
+      <c r="S80">
+        <v>3</v>
+      </c>
+      <c r="T80">
+        <v>1.52</v>
+      </c>
+      <c r="U80">
+        <v>2.4</v>
+      </c>
+      <c r="V80">
+        <v>3.27</v>
+      </c>
+      <c r="W80">
+        <v>1.32</v>
+      </c>
+      <c r="X80">
+        <v>7.7</v>
+      </c>
+      <c r="Y80">
+        <v>1.06</v>
+      </c>
+      <c r="Z80">
+        <v>3.5</v>
+      </c>
+      <c r="AA80">
+        <v>2.8</v>
+      </c>
+      <c r="AB80">
+        <v>2.2</v>
+      </c>
+      <c r="AC80">
+        <v>1.06</v>
+      </c>
+      <c r="AD80">
+        <v>7.5</v>
+      </c>
+      <c r="AE80">
+        <v>1.36</v>
+      </c>
+      <c r="AF80">
+        <v>2.88</v>
+      </c>
+      <c r="AG80">
+        <v>2.63</v>
+      </c>
+      <c r="AH80">
+        <v>1.44</v>
+      </c>
+      <c r="AI80">
+        <v>2.2</v>
+      </c>
+      <c r="AJ80">
+        <v>1.62</v>
+      </c>
+      <c r="AK80">
+        <v>1.72</v>
+      </c>
+      <c r="AL80">
+        <v>1.31</v>
+      </c>
+      <c r="AM80">
+        <v>1.2</v>
+      </c>
+      <c r="AN80">
+        <v>1.25</v>
+      </c>
+      <c r="AO80">
+        <v>1.75</v>
+      </c>
+      <c r="AP80">
+        <v>1</v>
+      </c>
+      <c r="AQ80">
+        <v>2</v>
+      </c>
+      <c r="AR80">
+        <v>1.3</v>
+      </c>
+      <c r="AS80">
+        <v>1.38</v>
+      </c>
+      <c r="AT80">
+        <v>2.68</v>
+      </c>
+      <c r="AU80">
+        <v>5</v>
+      </c>
+      <c r="AV80">
+        <v>7</v>
+      </c>
+      <c r="AW80">
+        <v>5</v>
+      </c>
+      <c r="AX80">
+        <v>6</v>
+      </c>
+      <c r="AY80">
+        <v>10</v>
+      </c>
+      <c r="AZ80">
+        <v>13</v>
+      </c>
+      <c r="BA80">
+        <v>2</v>
+      </c>
+      <c r="BB80">
+        <v>5</v>
+      </c>
+      <c r="BC80">
+        <v>7</v>
+      </c>
+      <c r="BD80">
+        <v>2.71</v>
+      </c>
+      <c r="BE80">
+        <v>7.7</v>
+      </c>
+      <c r="BF80">
+        <v>1.69</v>
+      </c>
+      <c r="BG80">
+        <v>1.36</v>
+      </c>
+      <c r="BH80">
+        <v>2.9</v>
+      </c>
+      <c r="BI80">
+        <v>1.64</v>
+      </c>
+      <c r="BJ80">
+        <v>2.23</v>
+      </c>
+      <c r="BK80">
+        <v>2.03</v>
+      </c>
+      <c r="BL80">
+        <v>1.77</v>
+      </c>
+      <c r="BM80">
+        <v>2.5</v>
+      </c>
+      <c r="BN80">
+        <v>1.48</v>
+      </c>
+      <c r="BO80">
+        <v>3.3</v>
+      </c>
+      <c r="BP80">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="81" spans="1:68">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>7729613</v>
+      </c>
+      <c r="C81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45680.45833333334</v>
+      </c>
+      <c r="F81">
+        <v>9</v>
+      </c>
+      <c r="G81" t="s">
+        <v>83</v>
+      </c>
+      <c r="H81" t="s">
+        <v>86</v>
+      </c>
+      <c r="I81">
+        <v>2</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>2</v>
+      </c>
+      <c r="L81">
+        <v>2</v>
+      </c>
+      <c r="M81">
+        <v>1</v>
+      </c>
+      <c r="N81">
+        <v>3</v>
+      </c>
+      <c r="O81" t="s">
+        <v>129</v>
+      </c>
+      <c r="P81" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q81">
+        <v>4.33</v>
+      </c>
+      <c r="R81">
+        <v>1.83</v>
+      </c>
+      <c r="S81">
+        <v>3</v>
+      </c>
+      <c r="T81">
+        <v>1.64</v>
+      </c>
+      <c r="U81">
+        <v>2.15</v>
+      </c>
+      <c r="V81">
+        <v>3.4</v>
+      </c>
+      <c r="W81">
+        <v>1.29</v>
+      </c>
+      <c r="X81">
+        <v>9</v>
+      </c>
+      <c r="Y81">
+        <v>1.04</v>
+      </c>
+      <c r="Z81">
+        <v>3.6</v>
+      </c>
+      <c r="AA81">
+        <v>2.7</v>
+      </c>
+      <c r="AB81">
+        <v>2.3</v>
+      </c>
+      <c r="AC81">
+        <v>1.1</v>
+      </c>
+      <c r="AD81">
+        <v>6.5</v>
+      </c>
+      <c r="AE81">
+        <v>1.53</v>
+      </c>
+      <c r="AF81">
+        <v>2.45</v>
+      </c>
+      <c r="AG81">
+        <v>2.7</v>
+      </c>
+      <c r="AH81">
+        <v>1.44</v>
+      </c>
+      <c r="AI81">
+        <v>2.25</v>
+      </c>
+      <c r="AJ81">
+        <v>1.62</v>
+      </c>
+      <c r="AK81">
+        <v>1.5</v>
+      </c>
+      <c r="AL81">
+        <v>1.36</v>
+      </c>
+      <c r="AM81">
+        <v>1.29</v>
+      </c>
+      <c r="AN81">
+        <v>1.25</v>
+      </c>
+      <c r="AO81">
+        <v>2</v>
+      </c>
+      <c r="AP81">
+        <v>1.6</v>
+      </c>
+      <c r="AQ81">
+        <v>1.6</v>
+      </c>
+      <c r="AR81">
+        <v>1.81</v>
+      </c>
+      <c r="AS81">
+        <v>1.51</v>
+      </c>
+      <c r="AT81">
+        <v>3.32</v>
+      </c>
+      <c r="AU81">
+        <v>4</v>
+      </c>
+      <c r="AV81">
+        <v>5</v>
+      </c>
+      <c r="AW81">
+        <v>9</v>
+      </c>
+      <c r="AX81">
+        <v>6</v>
+      </c>
+      <c r="AY81">
+        <v>13</v>
+      </c>
+      <c r="AZ81">
+        <v>11</v>
+      </c>
+      <c r="BA81">
+        <v>8</v>
+      </c>
+      <c r="BB81">
+        <v>8</v>
+      </c>
+      <c r="BC81">
+        <v>16</v>
+      </c>
+      <c r="BD81">
+        <v>0</v>
+      </c>
+      <c r="BE81">
+        <v>0</v>
+      </c>
+      <c r="BF81">
+        <v>0</v>
+      </c>
+      <c r="BG81">
+        <v>1.42</v>
+      </c>
+      <c r="BH81">
+        <v>2.62</v>
+      </c>
+      <c r="BI81">
+        <v>1.7</v>
+      </c>
+      <c r="BJ81">
+        <v>2.05</v>
+      </c>
+      <c r="BK81">
+        <v>2.1</v>
+      </c>
+      <c r="BL81">
+        <v>1.65</v>
+      </c>
+      <c r="BM81">
+        <v>2.7</v>
+      </c>
+      <c r="BN81">
+        <v>1.4</v>
+      </c>
+      <c r="BO81">
+        <v>3.6</v>
+      </c>
+      <c r="BP81">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Egypt Egyptian Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="169">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -406,6 +406,9 @@
     <t>['17', '37']</t>
   </si>
   <si>
+    <t>['87']</t>
+  </si>
+  <si>
     <t>['34', '45+4', '46']</t>
   </si>
   <si>
@@ -443,9 +446,6 @@
   </si>
   <si>
     <t>['45']</t>
-  </si>
-  <si>
-    <t>['87']</t>
   </si>
   <si>
     <t>['25']</t>
@@ -882,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP81"/>
+  <dimension ref="A1:BP82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1138,7 +1138,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q2">
         <v>4</v>
@@ -1344,7 +1344,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q3">
         <v>5</v>
@@ -1834,7 +1834,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5">
         <v>0.6</v>
@@ -1962,7 +1962,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q6">
         <v>3.6</v>
@@ -2168,7 +2168,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q7">
         <v>1.62</v>
@@ -2374,7 +2374,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2786,7 +2786,7 @@
         <v>92</v>
       </c>
       <c r="P10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -2992,7 +2992,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3404,7 +3404,7 @@
         <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q13">
         <v>5.5</v>
@@ -3610,7 +3610,7 @@
         <v>89</v>
       </c>
       <c r="P14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -3691,7 +3691,7 @@
         <v>1</v>
       </c>
       <c r="AQ14">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3816,7 +3816,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q15">
         <v>4.33</v>
@@ -4022,7 +4022,7 @@
         <v>96</v>
       </c>
       <c r="P16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q16">
         <v>5.5</v>
@@ -4846,7 +4846,7 @@
         <v>98</v>
       </c>
       <c r="P20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q20">
         <v>3.25</v>
@@ -5052,7 +5052,7 @@
         <v>99</v>
       </c>
       <c r="P21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5258,7 +5258,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="Q22">
         <v>1.91</v>
@@ -6366,7 +6366,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27">
         <v>2</v>
@@ -8429,7 +8429,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ37">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR37">
         <v>2.48</v>
@@ -9250,7 +9250,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ41">
         <v>1.8</v>
@@ -9996,7 +9996,7 @@
         <v>110</v>
       </c>
       <c r="P45" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q45">
         <v>5</v>
@@ -10489,7 +10489,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ47">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR47">
         <v>1.24</v>
@@ -13576,7 +13576,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ62">
         <v>0.25</v>
@@ -14322,7 +14322,7 @@
         <v>89</v>
       </c>
       <c r="P66" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q66">
         <v>6.5</v>
@@ -17569,6 +17569,212 @@
       </c>
       <c r="BP81">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:68">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>7729614</v>
+      </c>
+      <c r="C82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="2">
+        <v>45680.58333333334</v>
+      </c>
+      <c r="F82">
+        <v>9</v>
+      </c>
+      <c r="G82" t="s">
+        <v>73</v>
+      </c>
+      <c r="H82" t="s">
+        <v>76</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>1</v>
+      </c>
+      <c r="O82" t="s">
+        <v>130</v>
+      </c>
+      <c r="P82" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q82">
+        <v>4.33</v>
+      </c>
+      <c r="R82">
+        <v>1.83</v>
+      </c>
+      <c r="S82">
+        <v>3</v>
+      </c>
+      <c r="T82">
+        <v>1.61</v>
+      </c>
+      <c r="U82">
+        <v>2.21</v>
+      </c>
+      <c r="V82">
+        <v>3.62</v>
+      </c>
+      <c r="W82">
+        <v>1.26</v>
+      </c>
+      <c r="X82">
+        <v>10.2</v>
+      </c>
+      <c r="Y82">
+        <v>1.03</v>
+      </c>
+      <c r="Z82">
+        <v>3.6</v>
+      </c>
+      <c r="AA82">
+        <v>2.8</v>
+      </c>
+      <c r="AB82">
+        <v>2.15</v>
+      </c>
+      <c r="AC82">
+        <v>1.11</v>
+      </c>
+      <c r="AD82">
+        <v>5</v>
+      </c>
+      <c r="AE82">
+        <v>1.51</v>
+      </c>
+      <c r="AF82">
+        <v>2.46</v>
+      </c>
+      <c r="AG82">
+        <v>2.75</v>
+      </c>
+      <c r="AH82">
+        <v>1.4</v>
+      </c>
+      <c r="AI82">
+        <v>2.38</v>
+      </c>
+      <c r="AJ82">
+        <v>1.53</v>
+      </c>
+      <c r="AK82">
+        <v>1.85</v>
+      </c>
+      <c r="AL82">
+        <v>1.3</v>
+      </c>
+      <c r="AM82">
+        <v>1.16</v>
+      </c>
+      <c r="AN82">
+        <v>0.75</v>
+      </c>
+      <c r="AO82">
+        <v>2.33</v>
+      </c>
+      <c r="AP82">
+        <v>1.2</v>
+      </c>
+      <c r="AQ82">
+        <v>1.75</v>
+      </c>
+      <c r="AR82">
+        <v>1.26</v>
+      </c>
+      <c r="AS82">
+        <v>1.49</v>
+      </c>
+      <c r="AT82">
+        <v>2.75</v>
+      </c>
+      <c r="AU82">
+        <v>4</v>
+      </c>
+      <c r="AV82">
+        <v>4</v>
+      </c>
+      <c r="AW82">
+        <v>2</v>
+      </c>
+      <c r="AX82">
+        <v>9</v>
+      </c>
+      <c r="AY82">
+        <v>6</v>
+      </c>
+      <c r="AZ82">
+        <v>13</v>
+      </c>
+      <c r="BA82">
+        <v>2</v>
+      </c>
+      <c r="BB82">
+        <v>10</v>
+      </c>
+      <c r="BC82">
+        <v>12</v>
+      </c>
+      <c r="BD82">
+        <v>2.42</v>
+      </c>
+      <c r="BE82">
+        <v>7.4</v>
+      </c>
+      <c r="BF82">
+        <v>1.85</v>
+      </c>
+      <c r="BG82">
+        <v>1.38</v>
+      </c>
+      <c r="BH82">
+        <v>2.8</v>
+      </c>
+      <c r="BI82">
+        <v>1.7</v>
+      </c>
+      <c r="BJ82">
+        <v>2.13</v>
+      </c>
+      <c r="BK82">
+        <v>2.1</v>
+      </c>
+      <c r="BL82">
+        <v>1.71</v>
+      </c>
+      <c r="BM82">
+        <v>2.62</v>
+      </c>
+      <c r="BN82">
+        <v>1.42</v>
+      </c>
+      <c r="BO82">
+        <v>3.4</v>
+      </c>
+      <c r="BP82">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>
